--- a/outputs/daily/hr_rankings_2026-09-12_full.xlsx
+++ b/outputs/daily/hr_rankings_2026-09-12_full.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2786,34 +2786,30 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -3280,7 +3276,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3836,7 +3832,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -3893,7 +3889,7 @@
         <v>75</v>
       </c>
       <c r="U13" t="n">
-        <v>68.8</v>
+        <v>68</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -3945,12 +3941,12 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -5014,34 +5010,30 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5748,7 +5740,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -6094,34 +6086,30 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -6287,47 +6275,47 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>668804</t>
+          <t>680664</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bryan Reynolds</t>
+          <t>Eduardo Valencia</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-12T18:20:00Z</t>
+          <t>2026-09-12T17:10:00Z</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Clay Holmes</t>
+          <t>Tanner Gordon</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>605280</t>
+          <t>685299</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -6350,26 +6338,26 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>48.9</v>
+        <v>60.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>28.3</v>
+        <v>60</v>
       </c>
       <c r="R22" t="n">
-        <v>73.3</v>
+        <v>39.6</v>
       </c>
       <c r="S22" t="n">
-        <v>96.59999999999999</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U22" t="n">
-        <v>68.7</v>
+        <v>16.1</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
@@ -6383,7 +6371,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -6404,7 +6392,7 @@
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr"/>
@@ -6421,142 +6409,142 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/22, 0 HR</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 5.4% barrel, 7.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.4% barrel, 16.7 HR allowed</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>11.36</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>47.68</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>91.06</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>102.0216</t>
+          <t>101.389</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.4547</t>
+          <t>0.497</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>0.3548</t>
+          <t>0.323</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>72.62</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>28.23</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>40.01</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>23.9</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>0.1633</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>10.45</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>41.95</t>
+          <t>41.83</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>89.63</t>
+          <t>90.52</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>0.3765</t>
+          <t>0.4789</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
-          <t>0.1234</t>
+          <t>0.209</t>
         </is>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>18.27</t>
+          <t>33.32</t>
         </is>
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>Wrigley Field</t>
+          <t>Comerica Park</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr"/>
@@ -6567,56 +6555,56 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>642708</t>
+          <t>668804</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Amed Rosario</t>
+          <t>Bryan Reynolds</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-12T17:35:00Z</t>
+          <t>2026-09-12T18:20:00Z</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Zac Thornton</t>
+          <t>Clay Holmes</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>804267</t>
+          <t>605280</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>57.4</v>
+        <v>57.6</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -6630,26 +6618,26 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Good Environment, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>41.3</v>
+        <v>48.9</v>
       </c>
       <c r="Q23" t="n">
-        <v>46.9</v>
+        <v>28.3</v>
       </c>
       <c r="R23" t="n">
-        <v>78.2</v>
+        <v>73.3</v>
       </c>
       <c r="S23" t="n">
-        <v>86.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U23" t="n">
-        <v>34.2</v>
+        <v>68.7</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
@@ -6663,7 +6651,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -6684,7 +6672,7 @@
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr"/>
@@ -6706,22 +6694,22 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Contact streak: 8/23 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.0% barrel, 11.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 5.4% barrel, 7.7 HR allowed</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
@@ -6731,112 +6719,112 @@
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>9.36</t>
+          <t>11.36</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>42.48</t>
+          <t>47.68</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>90.92</t>
+          <t>91.06</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>101.6353</t>
+          <t>102.0216</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.4334</t>
+          <t>0.4547</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>0.1727</t>
+          <t>0.196</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>0.3177</t>
+          <t>0.3548</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>73.73</t>
+          <t>72.62</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>37.55</t>
+          <t>28.23</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>38.73</t>
+          <t>40.01</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>23.72</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>0.1747</t>
+          <t>0.1633</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>41.95</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>89.63</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>0.451</t>
+          <t>0.3765</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>0.1234</t>
         </is>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>18.27</t>
         </is>
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Wrigley Field</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr"/>
@@ -6847,27 +6835,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>680664</t>
+          <t>642708</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Eduardo Valencia</t>
+          <t>Amed Rosario</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-12T17:10:00Z</t>
+          <t>2026-09-12T17:35:00Z</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -6882,21 +6870,21 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Tanner Gordon</t>
+          <t>Zac Thornton</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>685299</t>
+          <t>804267</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>57.3</v>
+        <v>57.4</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -6910,26 +6898,26 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>60.1</v>
+        <v>41.3</v>
       </c>
       <c r="Q24" t="n">
-        <v>60</v>
+        <v>46.9</v>
       </c>
       <c r="R24" t="n">
-        <v>39.6</v>
+        <v>78.2</v>
       </c>
       <c r="S24" t="n">
         <v>86.40000000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U24" t="n">
-        <v>10.6</v>
+        <v>34.2</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
@@ -6964,7 +6952,7 @@
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr"/>
@@ -6981,12 +6969,12 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
@@ -6996,117 +6984,117 @@
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 0 HR</t>
+          <t>Contact streak: 8/23 over last 7 games</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.4% barrel, 16.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.0% barrel, 11.0 HR allowed</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>9.36</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>42.48</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>90.92</t>
         </is>
       </c>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>101.389</t>
+          <t>101.6353</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>0.497</t>
+          <t>0.4334</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.1727</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>0.323</t>
+          <t>0.3177</t>
         </is>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>73.73</t>
         </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>37.55</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>38.73</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>23.9</t>
+          <t>23.72</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.1747</t>
         </is>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>10.45</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>41.83</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>90.52</t>
+          <t>88.9</t>
         </is>
       </c>
       <c r="BD24" t="inlineStr">
         <is>
-          <t>0.4789</t>
+          <t>0.451</t>
         </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>0.184</t>
         </is>
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>33.32</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="BG24" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH24" t="inlineStr">
@@ -7116,7 +7104,7 @@
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>Comerica Park</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr"/>
@@ -7778,34 +7766,30 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -8276,7 +8260,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -9422,34 +9406,30 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10200,7 +10180,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -10546,34 +10526,30 @@
       </c>
       <c r="W37" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -11382,34 +11358,30 @@
       </c>
       <c r="W40" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 6</t>
-        </is>
-      </c>
+      <c r="AB40" t="inlineStr"/>
       <c r="AC40" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -13236,7 +13208,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -14378,34 +14350,30 @@
       </c>
       <c r="W51" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB51" t="inlineStr"/>
       <c r="AC51" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -14596,7 +14564,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -14876,7 +14844,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -17130,34 +17098,30 @@
       </c>
       <c r="W61" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y61" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 2</t>
-        </is>
-      </c>
+      <c r="AB61" t="inlineStr"/>
       <c r="AC61" t="inlineStr">
         <is>
           <t>H:2026 P:2026</t>
@@ -19827,47 +19791,47 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>679529</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Spencer Torkelson</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-09-12T23:10:00Z</t>
+          <t>2026-09-12T17:10:00Z</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Brady Singer</t>
+          <t>Tanner Gordon</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>663903</t>
+          <t>685299</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -19876,7 +19840,7 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>51.1</v>
+        <v>51.3</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
@@ -19890,62 +19854,58 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P71" t="n">
-        <v>39.1</v>
+        <v>47.5</v>
       </c>
       <c r="Q71" t="n">
-        <v>52.9</v>
+        <v>60</v>
       </c>
       <c r="R71" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S71" t="n">
-        <v>90.40000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="T71" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U71" t="n">
-        <v>28.9</v>
+        <v>35.6</v>
       </c>
       <c r="V71" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W71" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X71" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr"/>
       <c r="AC71" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -19970,7 +19930,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ71" t="inlineStr">
@@ -19980,119 +19940,127 @@
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 1 HR</t>
+          <t>Last 7 games: 4/17, 1 HR</t>
         </is>
       </c>
       <c r="AL71" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.5% barrel, 24.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.4% barrel, 16.7 HR allowed</t>
         </is>
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN71" t="inlineStr">
         <is>
-          <t>9.95</t>
+          <t>12.59</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>44.51</t>
+          <t>42.23</t>
         </is>
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>89.43</t>
+          <t>89.57</t>
         </is>
       </c>
       <c r="AQ71" t="inlineStr">
         <is>
-          <t>101.1477</t>
+          <t>100.1202</t>
         </is>
       </c>
       <c r="AR71" t="inlineStr">
         <is>
-          <t>0.4068</t>
+          <t>0.4119</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr">
         <is>
-          <t>0.1695</t>
+          <t>0.1957</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr">
         <is>
-          <t>0.3174</t>
+          <t>0.3165</t>
         </is>
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>73.16</t>
+          <t>73.14</t>
         </is>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
-          <t>32.39</t>
+          <t>26.16</t>
         </is>
       </c>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>34.52</t>
+          <t>47.49</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>18.88</t>
+          <t>35.9</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
-          <t>16.4</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>0.1607</t>
+          <t>0.1957</t>
         </is>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>10.45</t>
         </is>
       </c>
       <c r="BB71" t="inlineStr">
         <is>
-          <t>42.17</t>
+          <t>41.83</t>
         </is>
       </c>
       <c r="BC71" t="inlineStr">
         <is>
-          <t>90.86</t>
+          <t>90.52</t>
         </is>
       </c>
       <c r="BD71" t="inlineStr">
         <is>
-          <t>0.4391</t>
+          <t>0.4789</t>
         </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
-          <t>0.1751</t>
+          <t>0.209</t>
         </is>
       </c>
       <c r="BF71" t="inlineStr">
         <is>
-          <t>26.65</t>
-        </is>
-      </c>
-      <c r="BG71" t="inlineStr"/>
-      <c r="BH71" t="inlineStr"/>
+          <t>33.32</t>
+        </is>
+      </c>
+      <c r="BG71" t="inlineStr">
+        <is>
+          <t>In From RF</t>
+        </is>
+      </c>
+      <c r="BH71" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
       <c r="BI71" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Comerica Park</t>
         </is>
       </c>
       <c r="BJ71" t="inlineStr"/>
@@ -20103,47 +20071,47 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>679529</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spencer Torkelson</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-09-12T17:10:00Z</t>
+          <t>2026-09-12T23:10:00Z</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Tanner Gordon</t>
+          <t>Brady Singer</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>685299</t>
+          <t>663903</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -20152,7 +20120,7 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>50.9</v>
+        <v>51.1</v>
       </c>
       <c r="M72" t="inlineStr">
         <is>
@@ -20166,58 +20134,62 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P72" t="n">
-        <v>47.5</v>
+        <v>39.1</v>
       </c>
       <c r="Q72" t="n">
-        <v>60</v>
+        <v>52.9</v>
       </c>
       <c r="R72" t="n">
-        <v>39.6</v>
+        <v>27.6</v>
       </c>
       <c r="S72" t="n">
-        <v>64.3</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T72" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U72" t="n">
-        <v>28.5</v>
+        <v>28.9</v>
       </c>
       <c r="V72" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W72" t="inlineStr">
+      <c r="Z72" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X72" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y72" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC72" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -20237,12 +20209,12 @@
       </c>
       <c r="AH72" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ72" t="inlineStr">
@@ -20252,127 +20224,119 @@
       </c>
       <c r="AK72" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 1 HR</t>
+          <t>Last 7 games: 4/21, 1 HR</t>
         </is>
       </c>
       <c r="AL72" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.4% barrel, 16.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.5% barrel, 24.6 HR allowed</t>
         </is>
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN72" t="inlineStr">
         <is>
-          <t>12.59</t>
+          <t>9.95</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>42.23</t>
+          <t>44.51</t>
         </is>
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>89.57</t>
+          <t>89.43</t>
         </is>
       </c>
       <c r="AQ72" t="inlineStr">
         <is>
-          <t>100.1202</t>
+          <t>101.1477</t>
         </is>
       </c>
       <c r="AR72" t="inlineStr">
         <is>
-          <t>0.4119</t>
+          <t>0.4068</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr">
         <is>
-          <t>0.1957</t>
+          <t>0.1695</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr">
         <is>
-          <t>0.3165</t>
+          <t>0.3174</t>
         </is>
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>73.14</t>
+          <t>73.16</t>
         </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
-          <t>26.16</t>
+          <t>32.39</t>
         </is>
       </c>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>47.49</t>
+          <t>34.52</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>35.9</t>
+          <t>18.88</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>0.1957</t>
+          <t>0.1607</t>
         </is>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
-          <t>10.45</t>
+          <t>9.47</t>
         </is>
       </c>
       <c r="BB72" t="inlineStr">
         <is>
-          <t>41.83</t>
+          <t>42.17</t>
         </is>
       </c>
       <c r="BC72" t="inlineStr">
         <is>
-          <t>90.52</t>
+          <t>90.86</t>
         </is>
       </c>
       <c r="BD72" t="inlineStr">
         <is>
-          <t>0.4789</t>
+          <t>0.4391</t>
         </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>0.1751</t>
         </is>
       </c>
       <c r="BF72" t="inlineStr">
         <is>
-          <t>33.32</t>
-        </is>
-      </c>
-      <c r="BG72" t="inlineStr">
-        <is>
-          <t>In From RF</t>
-        </is>
-      </c>
-      <c r="BH72" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
+          <t>26.65</t>
+        </is>
+      </c>
+      <c r="BG72" t="inlineStr"/>
+      <c r="BH72" t="inlineStr"/>
       <c r="BI72" t="inlineStr">
         <is>
-          <t>Comerica Park</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ72" t="inlineStr"/>
@@ -23494,34 +23458,30 @@
       </c>
       <c r="W84" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X84" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y84" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB84" t="inlineStr"/>
       <c r="AC84" t="inlineStr">
         <is>
           <t>H:2026 P:2026</t>
@@ -24058,34 +24018,30 @@
       </c>
       <c r="W86" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X86" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y86" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB86" t="inlineStr"/>
       <c r="AC86" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -24622,34 +24578,30 @@
       </c>
       <c r="W88" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X88" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y88" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 2 vs RotoWire 3</t>
-        </is>
-      </c>
+      <c r="AB88" t="inlineStr"/>
       <c r="AC88" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -27646,34 +27598,30 @@
       </c>
       <c r="W99" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X99" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y99" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB99" t="inlineStr"/>
       <c r="AC99" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -27928,28 +27876,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W100" t="inlineStr"/>
-      <c r="X100" t="inlineStr"/>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="Y100" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB100" t="inlineStr"/>
       <c r="AC100" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -30023,27 +29975,27 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>703601</t>
+          <t>543760</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Max Clark</t>
+          <t>Marcus Semien</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-09-12T17:10:00Z</t>
+          <t>2026-09-12T17:35:00Z</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -30058,12 +30010,12 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Tanner Gordon</t>
+          <t>Gerrit Cole</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>685299</t>
+          <t>543037</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -30086,26 +30038,26 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Good Environment</t>
         </is>
       </c>
       <c r="P108" t="n">
-        <v>19</v>
+        <v>23.9</v>
       </c>
       <c r="Q108" t="n">
-        <v>60</v>
+        <v>46.9</v>
       </c>
       <c r="R108" t="n">
-        <v>39.6</v>
+        <v>78.2</v>
       </c>
       <c r="S108" t="n">
         <v>76.2</v>
       </c>
       <c r="T108" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U108" t="n">
-        <v>47.7</v>
+        <v>18</v>
       </c>
       <c r="V108" t="inlineStr">
         <is>
@@ -30140,7 +30092,7 @@
       <c r="AB108" t="inlineStr"/>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD108" t="inlineStr"/>
@@ -30162,127 +30114,127 @@
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/19, 1 HR</t>
+          <t>Last 7 games: 6/25, 0 HR</t>
         </is>
       </c>
       <c r="AL108" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.4% barrel, 16.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 17.0 HR allowed</t>
         </is>
       </c>
       <c r="AM108" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN108" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="AO108" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>34.09</t>
         </is>
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>87.11</t>
         </is>
       </c>
       <c r="AQ108" t="inlineStr">
         <is>
-          <t>98.2654</t>
+          <t>97.4281</t>
         </is>
       </c>
       <c r="AR108" t="inlineStr">
         <is>
-          <t>0.364</t>
+          <t>0.388</t>
         </is>
       </c>
       <c r="AS108" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>0.1425</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr">
         <is>
-          <t>0.318</t>
+          <t>0.3103</t>
         </is>
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>68.57</t>
         </is>
       </c>
       <c r="AV108" t="inlineStr">
         <is>
-          <t>27.5</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>37.8</t>
+          <t>46.91</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>0.1298</t>
         </is>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
-          <t>10.45</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="BB108" t="inlineStr">
         <is>
-          <t>41.83</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="BC108" t="inlineStr">
         <is>
-          <t>90.52</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="BD108" t="inlineStr">
         <is>
-          <t>0.4789</t>
+          <t>0.393</t>
         </is>
       </c>
       <c r="BE108" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>0.147</t>
         </is>
       </c>
       <c r="BF108" t="inlineStr">
         <is>
-          <t>33.32</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="BG108" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH108" t="inlineStr">
@@ -30292,7 +30244,7 @@
       </c>
       <c r="BI108" t="inlineStr">
         <is>
-          <t>Comerica Park</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ108" t="inlineStr"/>
@@ -30303,24 +30255,24 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>543760</t>
+          <t>683011</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Marcus Semien</t>
+          <t>Anthony Volpe</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
           <t>NYM</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>NYY</t>
-        </is>
-      </c>
       <c r="F109" t="inlineStr">
         <is>
           <t>2026-09-12T17:35:00Z</t>
@@ -30328,31 +30280,31 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Gerrit Cole</t>
+          <t>Zac Thornton</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>543037</t>
+          <t>804267</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L109" t="n">
-        <v>46.9</v>
+        <v>46.8</v>
       </c>
       <c r="M109" t="inlineStr">
         <is>
@@ -30366,11 +30318,11 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>Good Environment</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P109" t="n">
-        <v>23.9</v>
+        <v>23.7</v>
       </c>
       <c r="Q109" t="n">
         <v>46.9</v>
@@ -30379,13 +30331,13 @@
         <v>78.2</v>
       </c>
       <c r="S109" t="n">
-        <v>76.2</v>
+        <v>52.4</v>
       </c>
       <c r="T109" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U109" t="n">
-        <v>18</v>
+        <v>32.9</v>
       </c>
       <c r="V109" t="inlineStr">
         <is>
@@ -30399,7 +30351,7 @@
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y109" t="inlineStr">
@@ -30437,27 +30389,27 @@
       </c>
       <c r="AH109" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 0 HR</t>
+          <t>Last 7 games: 5/23, 1 HR</t>
         </is>
       </c>
       <c r="AL109" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 17.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.0% barrel, 11.0 HR allowed</t>
         </is>
       </c>
       <c r="AM109" t="inlineStr">
@@ -30467,97 +30419,97 @@
       </c>
       <c r="AN109" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>34.09</t>
+          <t>37.49</t>
         </is>
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>87.11</t>
+          <t>88.25</t>
         </is>
       </c>
       <c r="AQ109" t="inlineStr">
         <is>
-          <t>97.4281</t>
+          <t>98.806</t>
         </is>
       </c>
       <c r="AR109" t="inlineStr">
         <is>
-          <t>0.388</t>
+          <t>0.3483</t>
         </is>
       </c>
       <c r="AS109" t="inlineStr">
         <is>
-          <t>0.1425</t>
+          <t>0.1176</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr">
         <is>
-          <t>0.3103</t>
+          <t>0.2947</t>
         </is>
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>68.57</t>
+          <t>71.83</t>
         </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>20.38</t>
         </is>
       </c>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>46.91</t>
+          <t>31.61</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>23.43</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>0.1298</t>
+          <t>0.1202</t>
         </is>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB109" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="BC109" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>88.9</t>
         </is>
       </c>
       <c r="BD109" t="inlineStr">
         <is>
-          <t>0.393</t>
+          <t>0.451</t>
         </is>
       </c>
       <c r="BE109" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>0.184</t>
         </is>
       </c>
       <c r="BF109" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="BG109" t="inlineStr">
@@ -30583,47 +30535,47 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>683011</t>
+          <t>669134</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Anthony Volpe</t>
+          <t>Luis Campusano</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-09-12T17:35:00Z</t>
+          <t>2026-09-12T20:05:00Z</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Zac Thornton</t>
+          <t>Cesar Perdomo</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>804267</t>
+          <t>702885</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -30646,26 +30598,26 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>Good Environment, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P110" t="n">
-        <v>23.7</v>
+        <v>23.2</v>
       </c>
       <c r="Q110" t="n">
-        <v>46.9</v>
+        <v>26.4</v>
       </c>
       <c r="R110" t="n">
-        <v>78.2</v>
+        <v>61.3</v>
       </c>
       <c r="S110" t="n">
-        <v>52.4</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T110" t="n">
         <v>78</v>
       </c>
       <c r="U110" t="n">
-        <v>32.9</v>
+        <v>66.7</v>
       </c>
       <c r="V110" t="inlineStr">
         <is>
@@ -30679,7 +30631,7 @@
       </c>
       <c r="X110" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y110" t="inlineStr">
@@ -30717,142 +30669,142 @@
       </c>
       <c r="AH110" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/23, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL110" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.0% barrel, 11.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.0% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM110" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN110" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
-          <t>37.49</t>
+          <t>36.72</t>
         </is>
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>88.25</t>
+          <t>87.87</t>
         </is>
       </c>
       <c r="AQ110" t="inlineStr">
         <is>
-          <t>98.806</t>
+          <t>98.5477</t>
         </is>
       </c>
       <c r="AR110" t="inlineStr">
         <is>
-          <t>0.3483</t>
+          <t>0.3186</t>
         </is>
       </c>
       <c r="AS110" t="inlineStr">
         <is>
-          <t>0.1176</t>
+          <t>0.1211</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr">
         <is>
-          <t>0.2947</t>
+          <t>0.3032</t>
         </is>
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>71.83</t>
+          <t>72.89</t>
         </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
-          <t>20.38</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>31.61</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>20.78</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>0.1202</t>
+          <t>0.1288</t>
         </is>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB110" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="BC110" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="BD110" t="inlineStr">
         <is>
-          <t>0.451</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="BE110" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>0.139</t>
         </is>
       </c>
       <c r="BF110" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="BG110" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH110" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>62</t>
         </is>
       </c>
       <c r="BI110" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Oracle Park</t>
         </is>
       </c>
       <c r="BJ110" t="inlineStr"/>
@@ -30863,52 +30815,52 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>669134</t>
+          <t>680869</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Luis Campusano</t>
+          <t>Zack Gelof</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-09-12T20:05:00Z</t>
+          <t>2026-09-13T01:40:00Z</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Cesar Perdomo</t>
+          <t>Bryan Woo</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>702885</t>
+          <t>693433</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L111" t="n">
@@ -30926,65 +30878,65 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P111" t="n">
-        <v>23.2</v>
+        <v>39.8</v>
       </c>
       <c r="Q111" t="n">
-        <v>26.4</v>
+        <v>43</v>
       </c>
       <c r="R111" t="n">
-        <v>61.3</v>
+        <v>30.9</v>
       </c>
       <c r="S111" t="n">
-        <v>94.90000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T111" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U111" t="n">
-        <v>66.7</v>
+        <v>26.2</v>
       </c>
       <c r="V111" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X111" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W111" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X111" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y111" t="inlineStr">
+      <c r="Z111" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z111" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>RotoWire not confirmed</t>
+          <t>lineup projected / unconfirmed</t>
         </is>
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD111" t="inlineStr"/>
@@ -31001,142 +30953,134 @@
       </c>
       <c r="AH111" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI111" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/29, 1 HR</t>
         </is>
       </c>
       <c r="AL111" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.0% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.9% barrel, 20.4 HR allowed</t>
         </is>
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN111" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AO111" t="inlineStr">
         <is>
-          <t>36.72</t>
+          <t>43.91</t>
         </is>
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>87.87</t>
+          <t>88.94</t>
         </is>
       </c>
       <c r="AQ111" t="inlineStr">
         <is>
-          <t>98.5477</t>
+          <t>99.8453</t>
         </is>
       </c>
       <c r="AR111" t="inlineStr">
         <is>
-          <t>0.3186</t>
+          <t>0.3774</t>
         </is>
       </c>
       <c r="AS111" t="inlineStr">
         <is>
-          <t>0.1211</t>
+          <t>0.1739</t>
         </is>
       </c>
       <c r="AT111" t="inlineStr">
         <is>
-          <t>0.3032</t>
+          <t>0.2813</t>
         </is>
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>72.89</t>
+          <t>73.22</t>
         </is>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>27.01</t>
         </is>
       </c>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>20.78</t>
+          <t>28.43</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>0.1288</t>
+          <t>0.1722</t>
         </is>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="BB111" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>42.64</t>
         </is>
       </c>
       <c r="BC111" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>89.45</t>
         </is>
       </c>
       <c r="BD111" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.3814</t>
         </is>
       </c>
       <c r="BE111" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>0.1527</t>
         </is>
       </c>
       <c r="BF111" t="inlineStr">
         <is>
-          <t>32.0</t>
-        </is>
-      </c>
-      <c r="BG111" t="inlineStr">
-        <is>
-          <t>Out To CF</t>
-        </is>
-      </c>
-      <c r="BH111" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
+          <t>27.85</t>
+        </is>
+      </c>
+      <c r="BG111" t="inlineStr"/>
+      <c r="BH111" t="inlineStr"/>
       <c r="BI111" t="inlineStr">
         <is>
-          <t>Oracle Park</t>
+          <t>Sutter Health Park</t>
         </is>
       </c>
       <c r="BJ111" t="inlineStr"/>
@@ -31147,47 +31091,47 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>680869</t>
+          <t>703601</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Zack Gelof</t>
+          <t>Max Clark</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-09-13T01:40:00Z</t>
+          <t>2026-09-12T17:10:00Z</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Bryan Woo</t>
+          <t>Tanner Gordon</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>693433</t>
+          <t>685299</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -31196,7 +31140,7 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>46.8</v>
+        <v>46.7</v>
       </c>
       <c r="M112" t="inlineStr">
         <is>
@@ -31210,65 +31154,61 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P112" t="n">
-        <v>39.8</v>
+        <v>19</v>
       </c>
       <c r="Q112" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="R112" t="n">
-        <v>30.9</v>
+        <v>39.6</v>
       </c>
       <c r="S112" t="n">
-        <v>92.09999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="T112" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U112" t="n">
-        <v>26.2</v>
+        <v>45.3</v>
       </c>
       <c r="V112" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X112" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W112" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X112" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y112" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr"/>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD112" t="inlineStr"/>
@@ -31285,12 +31225,12 @@
       </c>
       <c r="AH112" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ112" t="inlineStr">
@@ -31300,119 +31240,127 @@
       </c>
       <c r="AK112" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/29, 1 HR</t>
+          <t>Last 7 games: 6/20, 1 HR</t>
         </is>
       </c>
       <c r="AL112" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.9% barrel, 20.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.4% barrel, 16.7 HR allowed</t>
         </is>
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN112" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
-          <t>43.91</t>
+          <t>39.8</t>
         </is>
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>88.94</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AQ112" t="inlineStr">
         <is>
-          <t>99.8453</t>
+          <t>98.2654</t>
         </is>
       </c>
       <c r="AR112" t="inlineStr">
         <is>
-          <t>0.3774</t>
+          <t>0.364</t>
         </is>
       </c>
       <c r="AS112" t="inlineStr">
         <is>
-          <t>0.1739</t>
+          <t>0.091</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr">
         <is>
-          <t>0.2813</t>
+          <t>0.318</t>
         </is>
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>73.22</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
-          <t>27.01</t>
+          <t>27.5</t>
         </is>
       </c>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>37.8</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>28.43</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>0.1722</t>
+          <t>0.172</t>
         </is>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>10.45</t>
         </is>
       </c>
       <c r="BB112" t="inlineStr">
         <is>
-          <t>42.64</t>
+          <t>41.83</t>
         </is>
       </c>
       <c r="BC112" t="inlineStr">
         <is>
-          <t>89.45</t>
+          <t>90.52</t>
         </is>
       </c>
       <c r="BD112" t="inlineStr">
         <is>
-          <t>0.3814</t>
+          <t>0.4789</t>
         </is>
       </c>
       <c r="BE112" t="inlineStr">
         <is>
-          <t>0.1527</t>
+          <t>0.209</t>
         </is>
       </c>
       <c r="BF112" t="inlineStr">
         <is>
-          <t>27.85</t>
-        </is>
-      </c>
-      <c r="BG112" t="inlineStr"/>
-      <c r="BH112" t="inlineStr"/>
+          <t>33.32</t>
+        </is>
+      </c>
+      <c r="BG112" t="inlineStr">
+        <is>
+          <t>In From RF</t>
+        </is>
+      </c>
+      <c r="BH112" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
       <c r="BI112" t="inlineStr">
         <is>
-          <t>Sutter Health Park</t>
+          <t>Comerica Park</t>
         </is>
       </c>
       <c r="BJ112" t="inlineStr"/>
@@ -33116,7 +33064,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -34818,34 +34766,30 @@
       </c>
       <c r="W125" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X125" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X125" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y125" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z125" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB125" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB125" t="inlineStr"/>
       <c r="AC125" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -35036,7 +34980,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -35150,7 +35094,7 @@
       </c>
       <c r="AI126" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ126" t="inlineStr">
@@ -35160,7 +35104,7 @@
       </c>
       <c r="AK126" t="inlineStr">
         <is>
-          <t>Last 7 games: 0/18, 0 HR</t>
+          <t>Last 7 games: 0/15, 0 HR</t>
         </is>
       </c>
       <c r="AL126" t="inlineStr">
@@ -35658,34 +35602,30 @@
       </c>
       <c r="W128" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X128" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z128" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X128" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y128" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z128" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB128" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 3</t>
-        </is>
-      </c>
+      <c r="AB128" t="inlineStr"/>
       <c r="AC128" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -36152,7 +36092,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -37294,34 +37234,30 @@
       </c>
       <c r="W134" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X134" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z134" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X134" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y134" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z134" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB134" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB134" t="inlineStr"/>
       <c r="AC134" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -37578,34 +37514,30 @@
       </c>
       <c r="W135" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X135" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z135" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X135" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y135" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z135" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB135" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB135" t="inlineStr"/>
       <c r="AC135" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -37862,34 +37794,30 @@
       </c>
       <c r="W136" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X136" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z136" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X136" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y136" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z136" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB136" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB136" t="inlineStr"/>
       <c r="AC136" t="inlineStr">
         <is>
           <t>H:2026 P:2026</t>
@@ -38700,28 +38628,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W139" t="inlineStr"/>
-      <c r="X139" t="inlineStr"/>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X139" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="Y139" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z139" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z139" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB139" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB139" t="inlineStr"/>
       <c r="AC139" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -38976,28 +38908,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W140" t="inlineStr"/>
-      <c r="X140" t="inlineStr"/>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X140" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="Y140" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z140" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z140" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB140" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB140" t="inlineStr"/>
       <c r="AC140" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -42318,34 +42254,30 @@
       </c>
       <c r="W152" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X152" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z152" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X152" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y152" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z152" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA152" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB152" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB152" t="inlineStr"/>
       <c r="AC152" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -43118,34 +43050,30 @@
       </c>
       <c r="W155" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X155" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z155" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X155" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y155" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z155" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB155" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB155" t="inlineStr"/>
       <c r="AC155" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -45874,34 +45802,30 @@
       </c>
       <c r="W165" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X165" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z165" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X165" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y165" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z165" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB165" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB165" t="inlineStr"/>
       <c r="AC165" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -46716,28 +46640,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W168" t="inlineStr"/>
-      <c r="X168" t="inlineStr"/>
+      <c r="W168" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X168" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="Y168" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z168" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z168" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA168" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB168" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB168" t="inlineStr"/>
       <c r="AC168" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -46994,34 +46922,30 @@
       </c>
       <c r="W169" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X169" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z169" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X169" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y169" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z169" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA169" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB169" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 2</t>
-        </is>
-      </c>
+      <c r="AB169" t="inlineStr"/>
       <c r="AC169" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -51694,34 +51618,30 @@
       </c>
       <c r="W186" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X186" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y186" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z186" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X186" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y186" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z186" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA186" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB186" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB186" t="inlineStr"/>
       <c r="AC186" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -53605,7 +53525,7 @@
         <v>78</v>
       </c>
       <c r="U193" t="n">
-        <v>21.8</v>
+        <v>20.8</v>
       </c>
       <c r="V193" t="inlineStr">
         <is>
@@ -53662,7 +53582,7 @@
       </c>
       <c r="AI193" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ193" t="inlineStr">
@@ -53672,7 +53592,7 @@
       </c>
       <c r="AK193" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/21, 1 HR</t>
+          <t>Last 7 games: 3/22, 1 HR</t>
         </is>
       </c>
       <c r="AL193" t="inlineStr">
@@ -54168,28 +54088,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W195" t="inlineStr"/>
-      <c r="X195" t="inlineStr"/>
+      <c r="W195" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X195" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="Y195" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z195" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z195" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA195" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB195" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB195" t="inlineStr"/>
       <c r="AC195" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -54722,34 +54646,30 @@
       </c>
       <c r="W197" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X197" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y197" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z197" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X197" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y197" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z197" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA197" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB197" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB197" t="inlineStr"/>
       <c r="AC197" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -55780,7 +55700,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -59464,28 +59384,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W214" t="inlineStr"/>
-      <c r="X214" t="inlineStr"/>
+      <c r="W214" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X214" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="Y214" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z214" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z214" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA214" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB214" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB214" t="inlineStr"/>
       <c r="AC214" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -64202,7 +64126,7 @@
       </c>
       <c r="AI231" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AJ231" t="inlineStr">
@@ -64212,7 +64136,7 @@
       </c>
       <c r="AK231" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/11, 0 HR</t>
+          <t>Last 7 games: 1/12, 0 HR</t>
         </is>
       </c>
       <c r="AL231" t="inlineStr">
@@ -65963,32 +65887,32 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>691182</t>
+          <t>630105</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Adael Amador</t>
+          <t>Jake Cronenworth</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>2026-09-12T17:10:00Z</t>
+          <t>2026-09-12T20:05:00Z</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -65998,12 +65922,12 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>Andrew Sears</t>
+          <t>Cesar Perdomo</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>808825</t>
+          <t>702885</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
@@ -66026,26 +65950,26 @@
       </c>
       <c r="O238" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P238" t="n">
-        <v>13.2</v>
+        <v>13.8</v>
       </c>
       <c r="Q238" t="n">
-        <v>26</v>
+        <v>26.4</v>
       </c>
       <c r="R238" t="n">
-        <v>39.6</v>
+        <v>61.3</v>
       </c>
       <c r="S238" t="n">
         <v>52.4</v>
       </c>
       <c r="T238" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U238" t="n">
-        <v>43.2</v>
+        <v>18.3</v>
       </c>
       <c r="V238" t="inlineStr">
         <is>
@@ -66097,12 +66021,12 @@
       </c>
       <c r="AH238" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI238" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ238" t="inlineStr">
@@ -66112,12 +66036,12 @@
       </c>
       <c r="AK238" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 1 HR</t>
+          <t>Last 7 games: 2/23, 1 HR</t>
         </is>
       </c>
       <c r="AL238" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 5.1% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.0% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM238" t="inlineStr">
@@ -66127,112 +66051,112 @@
       </c>
       <c r="AN238" t="inlineStr">
         <is>
-          <t>7.39</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="AO238" t="inlineStr">
         <is>
-          <t>26.52</t>
+          <t>31.44</t>
         </is>
       </c>
       <c r="AP238" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>87.38</t>
         </is>
       </c>
       <c r="AQ238" t="inlineStr">
         <is>
-          <t>97.0273</t>
+          <t>97.6166</t>
         </is>
       </c>
       <c r="AR238" t="inlineStr">
         <is>
-          <t>0.3158</t>
+          <t>0.311</t>
         </is>
       </c>
       <c r="AS238" t="inlineStr">
         <is>
-          <t>0.1097</t>
+          <t>0.0965</t>
         </is>
       </c>
       <c r="AT238" t="inlineStr">
         <is>
-          <t>0.2697</t>
+          <t>0.2847</t>
         </is>
       </c>
       <c r="AU238" t="inlineStr">
         <is>
-          <t>69.41</t>
+          <t>71.32</t>
         </is>
       </c>
       <c r="AV238" t="inlineStr">
         <is>
-          <t>8.92</t>
+          <t>17.04</t>
         </is>
       </c>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>31.61</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>27.54</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AZ238" t="inlineStr">
         <is>
-          <t>0.2238</t>
+          <t>0.096</t>
         </is>
       </c>
       <c r="BA238" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB238" t="inlineStr">
         <is>
-          <t>30.8</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="BC238" t="inlineStr">
         <is>
-          <t>90.1</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="BD238" t="inlineStr">
         <is>
-          <t>0.353</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="BE238" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>0.139</t>
         </is>
       </c>
       <c r="BF238" t="inlineStr">
         <is>
-          <t>35.9</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="BG238" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH238" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>62</t>
         </is>
       </c>
       <c r="BI238" t="inlineStr">
         <is>
-          <t>Comerica Park</t>
+          <t>Oracle Park</t>
         </is>
       </c>
       <c r="BJ238" t="inlineStr"/>
@@ -66243,32 +66167,32 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>630105</t>
+          <t>691182</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Jake Cronenworth</t>
+          <t>Adael Amador</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>2026-09-12T20:05:00Z</t>
+          <t>2026-09-12T17:10:00Z</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -66278,12 +66202,12 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>Cesar Perdomo</t>
+          <t>Andrew Sears</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>702885</t>
+          <t>808825</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
@@ -66292,7 +66216,7 @@
         </is>
       </c>
       <c r="L239" t="n">
-        <v>32.8</v>
+        <v>32.7</v>
       </c>
       <c r="M239" t="inlineStr">
         <is>
@@ -66306,26 +66230,26 @@
       </c>
       <c r="O239" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P239" t="n">
-        <v>13.8</v>
+        <v>13.2</v>
       </c>
       <c r="Q239" t="n">
-        <v>26.4</v>
+        <v>26</v>
       </c>
       <c r="R239" t="n">
-        <v>61.3</v>
+        <v>39.6</v>
       </c>
       <c r="S239" t="n">
         <v>52.4</v>
       </c>
       <c r="T239" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U239" t="n">
-        <v>18.3</v>
+        <v>41.2</v>
       </c>
       <c r="V239" t="inlineStr">
         <is>
@@ -66334,34 +66258,30 @@
       </c>
       <c r="W239" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X239" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y239" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z239" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X239" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y239" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z239" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA239" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB239" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 8 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AB239" t="inlineStr"/>
       <c r="AC239" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -66381,12 +66301,12 @@
       </c>
       <c r="AH239" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI239" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ239" t="inlineStr">
@@ -66396,12 +66316,12 @@
       </c>
       <c r="AK239" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/23, 1 HR</t>
+          <t>Last 7 games: 6/22, 1 HR</t>
         </is>
       </c>
       <c r="AL239" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.0% barrel, 1.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 5.1% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM239" t="inlineStr">
@@ -66411,112 +66331,112 @@
       </c>
       <c r="AN239" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>7.39</t>
         </is>
       </c>
       <c r="AO239" t="inlineStr">
         <is>
-          <t>31.44</t>
+          <t>26.52</t>
         </is>
       </c>
       <c r="AP239" t="inlineStr">
         <is>
-          <t>87.38</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AQ239" t="inlineStr">
         <is>
-          <t>97.6166</t>
+          <t>97.0273</t>
         </is>
       </c>
       <c r="AR239" t="inlineStr">
         <is>
-          <t>0.311</t>
+          <t>0.3158</t>
         </is>
       </c>
       <c r="AS239" t="inlineStr">
         <is>
-          <t>0.0965</t>
+          <t>0.1097</t>
         </is>
       </c>
       <c r="AT239" t="inlineStr">
         <is>
-          <t>0.2847</t>
+          <t>0.2697</t>
         </is>
       </c>
       <c r="AU239" t="inlineStr">
         <is>
-          <t>71.32</t>
+          <t>69.41</t>
         </is>
       </c>
       <c r="AV239" t="inlineStr">
         <is>
-          <t>17.04</t>
+          <t>8.92</t>
         </is>
       </c>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>31.61</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>27.54</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="AZ239" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>0.2238</t>
         </is>
       </c>
       <c r="BA239" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="BB239" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>30.8</t>
         </is>
       </c>
       <c r="BC239" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>90.1</t>
         </is>
       </c>
       <c r="BD239" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.353</t>
         </is>
       </c>
       <c r="BE239" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>0.136</t>
         </is>
       </c>
       <c r="BF239" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>35.9</t>
         </is>
       </c>
       <c r="BG239" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH239" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI239" t="inlineStr">
         <is>
-          <t>Oracle Park</t>
+          <t>Comerica Park</t>
         </is>
       </c>
       <c r="BJ239" t="inlineStr"/>
@@ -67174,34 +67094,30 @@
       </c>
       <c r="W242" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X242" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y242" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z242" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X242" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y242" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z242" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA242" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB242" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 9 vs RotoWire 8</t>
-        </is>
-      </c>
+      <c r="AB242" t="inlineStr"/>
       <c r="AC242" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -67966,34 +67882,30 @@
       </c>
       <c r="W245" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X245" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y245" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z245" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X245" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y245" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z245" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA245" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB245" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 8 vs RotoWire 9</t>
-        </is>
-      </c>
+      <c r="AB245" t="inlineStr"/>
       <c r="AC245" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -70894,34 +70806,30 @@
       </c>
       <c r="W256" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X256" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y256" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z256" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X256" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y256" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z256" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA256" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB256" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 9 vs RotoWire 8</t>
-        </is>
-      </c>
+      <c r="AB256" t="inlineStr"/>
       <c r="AC256" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -71176,28 +71084,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W257" t="inlineStr"/>
-      <c r="X257" t="inlineStr"/>
+      <c r="W257" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X257" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="Y257" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z257" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z257" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA257" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB257" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB257" t="inlineStr"/>
       <c r="AC257" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -73106,7 +73018,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -73386,7 +73298,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -74786,7 +74698,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -75132,34 +75044,30 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -75626,7 +75534,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -76182,7 +76090,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -76239,7 +76147,7 @@
         <v>75</v>
       </c>
       <c r="U13" t="n">
-        <v>68.8</v>
+        <v>68</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -76291,12 +76199,12 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -77360,34 +77268,30 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -78094,7 +77998,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -78440,34 +78344,30 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
